--- a/studySpecific/ENSEMBLE/要件定義書_CombineProcess.xlsx
+++ b/studySpecific/ENSEMBLE/要件定義書_CombineProcess.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Local\iTMS\SDTM_ENSEMBLE\studySpecific\ENSEMBLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECE8B045-CBC2-4A5E-8202-E997097E5A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760E4E9B-6B42-4BCD-89C7-CB517B8A1FED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27375" yWindow="1425" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -968,9 +968,6 @@
     <t>e449ccc</t>
   </si>
   <si>
-    <t>WIP</t>
-  </si>
-  <si>
     <t>0.1</t>
   </si>
   <si>
@@ -993,7 +990,64 @@
     <phoneticPr fontId="7"/>
   </si>
   <si>
-    <t>張　泊江（Group A）</t>
+    <t>・Group A/B相互検証のため、要件-設計-実装-試験を追跡可能にする必要がある。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>抽出結果で全行空白の項目を出力から除外すること。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>ENSEMBLE研究では、入力整形工程から標準マッピング工程に至る変換の中で、 設定ファイルのみでは表現できない研究固有の業務ロジックが存在する。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>この不足部分を研究固有関数で補完し、後続のSDTM変換品質を担保する。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>3. 前後工程連携における研究固有ロジックの再現性・追跡性確保。</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">・対象機能: 研究固有関数: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>filter_df_by_field, DM</t>
+    </r>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>・対象連携点: 上位工程からの研究固有関数呼び出し</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>上位工程連携</t>
+  </si>
+  <si>
+    <t>上位工程から研究固有関数が呼び出せること。</t>
+  </si>
+  <si>
+    <t>工程連携要件・受入基準・追跡運用ルール整備に加え、要件段階を実装非依存化（関数名中心、モジュール/ファイル名および上下流実装参照を除外）してWIP変更を統合</t>
+  </si>
+  <si>
+    <t>張　泊江</t>
+  </si>
+  <si>
+    <t>96985d9</t>
+    <phoneticPr fontId="7"/>
+  </si>
+  <si>
+    <t>張　泊江</t>
     <rPh sb="0" eb="1">
       <t>ハリ</t>
     </rPh>
@@ -1004,59 +1058,6 @@
       <t>エ</t>
     </rPh>
     <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>・Group A/B相互検証のため、要件-設計-実装-試験を追跡可能にする必要がある。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>抽出結果で全行空白の項目を出力から除外すること。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>ENSEMBLE研究では、入力整形工程から標準マッピング工程に至る変換の中で、 設定ファイルのみでは表現できない研究固有の業務ロジックが存在する。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>この不足部分を研究固有関数で補完し、後続のSDTM変換品質を担保する。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>3. 前後工程連携における研究固有ロジックの再現性・追跡性確保。</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">・対象機能: 研究固有関数: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>filter_df_by_field, DM</t>
-    </r>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>・対象連携点: 上位工程からの研究固有関数呼び出し</t>
-    <phoneticPr fontId="7"/>
-  </si>
-  <si>
-    <t>上位工程連携</t>
-  </si>
-  <si>
-    <t>上位工程から研究固有関数が呼び出せること。</t>
-  </si>
-  <si>
-    <t>工程連携要件・受入基準・追跡運用ルール整備に加え、要件段階を実装非依存化（関数名中心、モジュール/ファイル名および上下流実装参照を除外）してWIP変更を統合</t>
-  </si>
-  <si>
-    <t>張　泊江</t>
   </si>
 </sst>
 </file>
@@ -1336,11 +1337,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1350,6 +1346,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1714,7 +1715,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.15">
@@ -1803,7 +1804,7 @@
     </row>
     <row r="4" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A4" s="23" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B4" s="18">
         <v>46055</v>
@@ -1812,7 +1813,7 @@
         <v>160</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E4" s="19" t="s">
         <v>162</v>
@@ -1820,7 +1821,7 @@
     </row>
     <row r="5" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A5" s="24" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B5" s="18">
         <v>46055</v>
@@ -1829,7 +1830,7 @@
         <v>163</v>
       </c>
       <c r="D5" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E5" s="19" t="s">
         <v>164</v>
@@ -1837,7 +1838,7 @@
     </row>
     <row r="6" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A6" s="24" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B6" s="18">
         <v>46066</v>
@@ -1846,7 +1847,7 @@
         <v>165</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>166</v>
@@ -1854,7 +1855,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="26" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B7" s="18">
         <v>46066</v>
@@ -1863,7 +1864,7 @@
         <v>167</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>168</v>
@@ -1871,7 +1872,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="26" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B8" s="18">
         <v>46066</v>
@@ -1880,27 +1881,27 @@
         <v>169</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="40.5" x14ac:dyDescent="0.15">
-      <c r="A9" s="30" t="s">
-        <v>177</v>
+      <c r="A9" s="27" t="s">
+        <v>176</v>
       </c>
       <c r="B9" s="18">
         <v>46073</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="29" t="s">
         <v>189</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -1923,30 +1924,30 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
@@ -1965,25 +1966,25 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="32"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B15" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.15">
@@ -2016,12 +2017,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
@@ -2039,12 +2040,12 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="32"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B9" t="s">
@@ -2058,7 +2059,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="B11" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -2088,12 +2089,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
@@ -2131,7 +2132,7 @@
         <v>40</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
@@ -2152,12 +2153,12 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
@@ -2230,12 +2231,12 @@
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
@@ -2256,10 +2257,10 @@
         <v>89</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>14</v>
@@ -2307,12 +2308,12 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="29"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
@@ -2371,10 +2372,10 @@
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="29"/>
+      <c r="B9" s="32"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
